--- a/diseases/d217/2010-2014.xlsx
+++ b/diseases/d217/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d217/2010-2014.xlsx
+++ b/diseases/d217/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d217/2010-2014.xlsx
+++ b/diseases/d217/2010-2014.xlsx
@@ -768,9 +768,6 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1020,7 +1017,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1170,9 +1167,6 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1422,7 +1416,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1572,9 +1566,6 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1824,7 +1815,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1974,9 +1965,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2226,7 +2214,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2376,9 +2364,6 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2628,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2778,9 +2763,6 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3030,7 +3012,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3180,9 +3162,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3432,7 +3411,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3582,9 +3561,6 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3834,7 +3810,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3984,9 +3960,6 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4236,7 +4209,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4386,9 +4359,6 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4638,7 +4608,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4788,9 +4758,6 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5040,7 +5007,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5190,9 +5157,6 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5442,7 +5406,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5592,9 +5556,6 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5844,7 +5805,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -5994,9 +5955,6 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6246,7 +6204,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6396,9 +6354,6 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6648,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6798,9 +6753,6 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7050,7 +7002,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7200,9 +7152,6 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7452,7 +7401,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7602,9 +7551,6 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7854,7 +7800,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8004,9 +7950,6 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8256,7 +8199,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8406,9 +8349,6 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8658,7 +8598,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8808,9 +8748,6 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -9060,7 +8997,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9210,9 +9147,6 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9462,7 +9396,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9612,9 +9546,6 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9864,7 +9795,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10014,9 +9945,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -10266,7 +10194,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10416,9 +10344,6 @@
       <c r="P50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10668,7 +10593,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10818,9 +10743,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -11070,7 +10992,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11220,9 +11142,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11472,7 +11391,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,9 +11541,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11874,7 +11790,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12024,9 +11940,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -12276,7 +12189,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12426,9 +12339,6 @@
       <c r="P60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12678,7 +12588,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12828,9 +12738,6 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13080,7 +12987,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13230,9 +13137,6 @@
       <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -13482,7 +13386,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13632,9 +13536,6 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13884,7 +13785,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14034,9 +13935,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -14286,7 +14184,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14436,9 +14334,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14688,7 +14583,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14838,9 +14733,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -15090,7 +14982,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15240,9 +15132,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -15492,7 +15381,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15642,9 +15531,6 @@
       <c r="P76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15894,7 +15780,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16044,9 +15930,6 @@
       <c r="P78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -16296,7 +16179,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16446,9 +16329,6 @@
       <c r="P80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -16698,7 +16578,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16848,9 +16728,6 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -17100,7 +16977,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17250,9 +17127,6 @@
       <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -17502,7 +17376,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17652,9 +17526,6 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -17904,7 +17775,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18054,9 +17925,6 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -18306,7 +18174,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18456,9 +18324,6 @@
       <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -18708,7 +18573,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18858,9 +18723,6 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -19110,7 +18972,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19260,9 +19122,6 @@
       <c r="P94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -19512,7 +19371,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19662,9 +19521,6 @@
       <c r="P96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -19914,7 +19770,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20064,9 +19920,6 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -20316,7 +20169,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20466,9 +20319,6 @@
       <c r="P100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -20718,7 +20568,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20868,9 +20718,6 @@
       <c r="P102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -21120,7 +20967,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21270,9 +21117,6 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -21522,7 +21366,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21672,9 +21516,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -21924,7 +21765,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22074,9 +21915,6 @@
       <c r="P108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -22326,7 +22164,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22476,9 +22314,6 @@
       <c r="P110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -22728,7 +22563,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22878,9 +22713,6 @@
       <c r="P112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -23130,7 +22962,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23280,9 +23112,6 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -23532,7 +23361,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23682,9 +23511,6 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -23934,7 +23760,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24084,9 +23910,6 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -24336,7 +24159,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24486,9 +24309,6 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -24738,7 +24558,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24888,9 +24708,6 @@
       <c r="P122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -25140,7 +24957,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25290,9 +25107,6 @@
       <c r="P124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -25542,7 +25356,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25692,9 +25506,6 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -25944,7 +25755,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26094,9 +25905,6 @@
       <c r="P128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -26346,7 +26154,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26496,9 +26304,6 @@
       <c r="P130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -26748,7 +26553,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26898,9 +26703,6 @@
       <c r="P132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -27150,7 +26952,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27300,9 +27102,6 @@
       <c r="P134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -27552,7 +27351,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27702,9 +27501,6 @@
       <c r="P136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -27954,7 +27750,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28104,9 +27900,6 @@
       <c r="P138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -28356,7 +28149,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28506,9 +28299,6 @@
       <c r="P140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -28758,7 +28548,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28908,9 +28698,6 @@
       <c r="P142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -29160,7 +28947,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29310,9 +29097,6 @@
       <c r="P144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -29562,7 +29346,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29712,9 +29496,6 @@
       <c r="P146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -29964,7 +29745,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30114,9 +29895,6 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -30366,7 +30144,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30516,9 +30294,6 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -30768,7 +30543,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30918,9 +30693,6 @@
       <c r="P152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -31170,7 +30942,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31320,9 +31092,6 @@
       <c r="P154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -31572,7 +31341,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31722,9 +31491,6 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -31974,7 +31740,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32124,9 +31890,6 @@
       <c r="P158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -32376,7 +32139,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32526,9 +32289,6 @@
       <c r="P160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -32778,7 +32538,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32928,9 +32688,6 @@
       <c r="P162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -33180,7 +32937,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33330,9 +33087,6 @@
       <c r="P164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -33582,7 +33336,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33732,9 +33486,6 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -33984,7 +33735,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34134,9 +33885,6 @@
       <c r="P168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -34386,7 +34134,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34536,9 +34284,6 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -34788,7 +34533,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34938,9 +34683,6 @@
       <c r="P172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -35190,7 +34932,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35340,9 +35082,6 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -35592,7 +35331,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35742,9 +35481,6 @@
       <c r="P176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -35994,7 +35730,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36144,9 +35880,6 @@
       <c r="P178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -36396,7 +36129,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36546,9 +36279,6 @@
       <c r="P180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -36798,7 +36528,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36948,9 +36678,6 @@
       <c r="P182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -37200,7 +36927,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37350,9 +37077,6 @@
       <c r="P184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -37602,7 +37326,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37752,9 +37476,6 @@
       <c r="P186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -38004,7 +37725,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38154,9 +37875,6 @@
       <c r="P188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -38406,7 +38124,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38556,9 +38274,6 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -38808,7 +38523,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38958,9 +38673,6 @@
       <c r="P192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -39210,7 +38922,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39360,9 +39072,6 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -39612,7 +39321,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39762,9 +39471,6 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -40014,7 +39720,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40164,9 +39870,6 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -40416,7 +40119,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40566,9 +40269,6 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -40818,7 +40518,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40968,9 +40668,6 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -41220,7 +40917,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41370,9 +41067,6 @@
       <c r="P204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -41622,7 +41316,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41772,9 +41466,6 @@
       <c r="P206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -42024,7 +41715,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42174,9 +41865,6 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -42426,7 +42114,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -42576,9 +42264,6 @@
       <c r="P210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -42828,7 +42513,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42978,9 +42663,6 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -43230,7 +42912,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43380,9 +43062,6 @@
       <c r="P214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -43632,7 +43311,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43782,9 +43461,6 @@
       <c r="P216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -44034,7 +43710,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -44184,9 +43860,6 @@
       <c r="P218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -44436,7 +44109,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44586,9 +44259,6 @@
       <c r="P220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -44838,7 +44508,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44988,9 +44658,6 @@
       <c r="P222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -45240,7 +44907,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45390,9 +45057,6 @@
       <c r="P224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -45642,7 +45306,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45792,9 +45456,6 @@
       <c r="P226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -46044,7 +45705,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46194,9 +45855,6 @@
       <c r="P228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -46446,7 +46104,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -46596,9 +46254,6 @@
       <c r="P230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -46848,7 +46503,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46998,9 +46653,6 @@
       <c r="P232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -47250,7 +46902,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -47400,9 +47052,6 @@
       <c r="P234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -47652,7 +47301,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47802,9 +47451,6 @@
       <c r="P236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -48054,7 +47700,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -48204,9 +47850,6 @@
       <c r="P238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -48456,7 +48099,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48606,9 +48249,6 @@
       <c r="P240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -48858,7 +48498,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">

--- a/diseases/d217/2010-2014.xlsx
+++ b/diseases/d217/2010-2014.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34124,7 +34124,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34523,7 +34523,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35321,7 +35321,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36518,7 +36518,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36917,7 +36917,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38513,7 +38513,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38912,7 +38912,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39311,7 +39311,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39710,7 +39710,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40109,7 +40109,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40907,7 +40907,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41705,7 +41705,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42503,7 +42503,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42902,7 +42902,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43301,7 +43301,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44099,7 +44099,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44897,7 +44897,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45296,7 +45296,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45695,7 +45695,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46094,7 +46094,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47291,7 +47291,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47690,7 +47690,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48089,7 +48089,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d217/2010-2014.xlsx
+++ b/diseases/d217/2010-2014.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34124,7 +34124,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34523,7 +34523,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35321,7 +35321,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36518,7 +36518,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36917,7 +36917,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38513,7 +38513,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38912,7 +38912,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39311,7 +39311,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39710,7 +39710,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40109,7 +40109,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40907,7 +40907,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41705,7 +41705,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42503,7 +42503,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42902,7 +42902,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43301,7 +43301,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44099,7 +44099,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44897,7 +44897,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45296,7 +45296,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45695,7 +45695,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46094,7 +46094,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47291,7 +47291,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47690,7 +47690,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48089,7 +48089,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d217/2010-2014.xlsx
+++ b/diseases/d217/2010-2014.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34124,7 +34124,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34523,7 +34523,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35321,7 +35321,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36518,7 +36518,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36917,7 +36917,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38513,7 +38513,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38912,7 +38912,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39311,7 +39311,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39710,7 +39710,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40109,7 +40109,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40907,7 +40907,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41705,7 +41705,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42503,7 +42503,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42902,7 +42902,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43301,7 +43301,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44099,7 +44099,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44897,7 +44897,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45296,7 +45296,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45695,7 +45695,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46094,7 +46094,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47291,7 +47291,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47690,7 +47690,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48089,7 +48089,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d217/2010-2014.xlsx
+++ b/diseases/d217/2010-2014.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34124,7 +34124,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34523,7 +34523,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35321,7 +35321,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36518,7 +36518,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36917,7 +36917,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38513,7 +38513,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38912,7 +38912,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39311,7 +39311,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39710,7 +39710,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40109,7 +40109,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -40907,7 +40907,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41705,7 +41705,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42503,7 +42503,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42902,7 +42902,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43301,7 +43301,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44099,7 +44099,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44897,7 +44897,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45296,7 +45296,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45695,7 +45695,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46094,7 +46094,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47291,7 +47291,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47690,7 +47690,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48089,7 +48089,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
